--- a/Project_ETF/ETF_Investment_Portfolio/00981A/ETF_Investment_Portfolio_20260616.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/00981A/ETF_Investment_Portfolio_20260616.xlsx
@@ -1525,17 +1525,17 @@
     <row r="63">
       <c r="A63" s="3" t="inlineStr">
         <is>
-          <t>1815</t>
+          <t>2382</t>
         </is>
       </c>
       <c r="B63" s="3" t="inlineStr">
         <is>
-          <t>富喬</t>
+          <t>廣達</t>
         </is>
       </c>
       <c r="C63" s="4" t="inlineStr">
         <is>
-          <t>107,000</t>
+          <t>1,000</t>
         </is>
       </c>
       <c r="D63" s="4" t="inlineStr">
@@ -1547,17 +1547,17 @@
     <row r="64">
       <c r="A64" s="3" t="inlineStr">
         <is>
-          <t>2382</t>
+          <t>2439</t>
         </is>
       </c>
       <c r="B64" s="3" t="inlineStr">
         <is>
-          <t>廣達</t>
+          <t>美律</t>
         </is>
       </c>
       <c r="C64" s="4" t="inlineStr">
         <is>
-          <t>1,000</t>
+          <t>18,000</t>
         </is>
       </c>
       <c r="D64" s="4" t="inlineStr">
@@ -1569,17 +1569,17 @@
     <row r="65">
       <c r="A65" s="3" t="inlineStr">
         <is>
-          <t>2481</t>
+          <t>3264</t>
         </is>
       </c>
       <c r="B65" s="3" t="inlineStr">
         <is>
-          <t>強茂</t>
+          <t>欣銓</t>
         </is>
       </c>
       <c r="C65" s="4" t="inlineStr">
         <is>
-          <t>5,000</t>
+          <t>1,000</t>
         </is>
       </c>
       <c r="D65" s="4" t="inlineStr">
@@ -1591,17 +1591,17 @@
     <row r="66">
       <c r="A66" s="3" t="inlineStr">
         <is>
-          <t>3008</t>
+          <t>2481</t>
         </is>
       </c>
       <c r="B66" s="3" t="inlineStr">
         <is>
-          <t>大立光</t>
+          <t>強茂</t>
         </is>
       </c>
       <c r="C66" s="4" t="inlineStr">
         <is>
-          <t>1,000</t>
+          <t>5,000</t>
         </is>
       </c>
       <c r="D66" s="4" t="inlineStr">
@@ -1613,17 +1613,17 @@
     <row r="67">
       <c r="A67" s="3" t="inlineStr">
         <is>
-          <t>2439</t>
+          <t>3008</t>
         </is>
       </c>
       <c r="B67" s="3" t="inlineStr">
         <is>
-          <t>美律</t>
+          <t>大立光</t>
         </is>
       </c>
       <c r="C67" s="4" t="inlineStr">
         <is>
-          <t>18,000</t>
+          <t>1,000</t>
         </is>
       </c>
       <c r="D67" s="4" t="inlineStr">
@@ -1635,17 +1635,17 @@
     <row r="68">
       <c r="A68" s="3" t="inlineStr">
         <is>
-          <t>3264</t>
+          <t>1815</t>
         </is>
       </c>
       <c r="B68" s="3" t="inlineStr">
         <is>
-          <t>欣銓</t>
+          <t>富喬</t>
         </is>
       </c>
       <c r="C68" s="4" t="inlineStr">
         <is>
-          <t>1,000</t>
+          <t>107,000</t>
         </is>
       </c>
       <c r="D68" s="4" t="inlineStr">
